--- a/artfynd/A 13274-2022 artfynd.xlsx
+++ b/artfynd/A 13274-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13274-2022 artfynd.xlsx
+++ b/artfynd/A 13274-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87182185</v>
+        <v>87182263</v>
       </c>
       <c r="B2" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -719,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>307144.4783613119</v>
+        <v>307023</v>
       </c>
       <c r="R2" t="n">
-        <v>6514206.862337788</v>
+        <v>6514142</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +743,9 @@
           <t>2020-07-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +776,7 @@
         <v>87182207</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>307067.2536337067</v>
+        <v>307067</v>
       </c>
       <c r="R3" t="n">
-        <v>6514152.447408848</v>
+        <v>6514152</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +845,9 @@
           <t>2020-07-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-07-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,6 +872,108 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>87182185</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>N om Älgetjärnet, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>307144</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6514207</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Naverstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-07-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-07-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13274-2022 artfynd.xlsx
+++ b/artfynd/A 13274-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87182263</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87182207</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,8 +989,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87182185</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>